--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136480652</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136480614</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136480594</v>
       </c>
       <c r="B5" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>136480597</v>
       </c>
       <c r="B6" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>136480812</v>
       </c>
       <c r="B7" t="n">
-        <v>58729</v>
+        <v>58731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130659216</v>
+        <v>137154287</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>56882</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,38 +816,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+          <t>Sika, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707203</v>
+        <v>707243</v>
       </c>
       <c r="R3" t="n">
-        <v>6624704</v>
+        <v>6624705</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,12 +889,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>22:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>22:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,12 +919,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Indre Cepukaite</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -909,38 +934,38 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130659216</t>
+          <t>https://artportalen.se/Sighting/137154287</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136480614</v>
+        <v>137154292</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>56882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,24 +973,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+          <t>Sika, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707152</v>
+        <v>707228</v>
       </c>
       <c r="R4" t="n">
-        <v>6624756</v>
+        <v>6624661</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +1024,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,31 +1054,31 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Fågelinventering Sika 2026</t>
+          <t>NVI Sika 4:37</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136480614</t>
+          <t>https://artportalen.se/Sighting/137154292</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136480594</v>
+        <v>137154385</v>
       </c>
       <c r="B5" t="n">
-        <v>58164</v>
+        <v>56882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,46 +1086,56 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103023</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+          <t>Sika, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707188</v>
+        <v>707174</v>
       </c>
       <c r="R5" t="n">
-        <v>6624740</v>
+        <v>6624767</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,22 +1159,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>04:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,31 +1189,31 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Fågelinventering Sika 2026</t>
+          <t>NVI Sika 4:37</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136480594</t>
+          <t>https://artportalen.se/Sighting/137154385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136480597</v>
+        <v>130659216</v>
       </c>
       <c r="B6" t="n">
-        <v>58164</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,16 +1221,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103023</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,24 +1243,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707213</v>
+        <v>707203</v>
       </c>
       <c r="R6" t="n">
-        <v>6624684</v>
+        <v>6624704</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1279,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:51</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:51</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,26 +1304,26 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Via Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Fågelinventering Sika 2026</t>
+          <t>NVI Sika 4:37</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136480597</t>
+          <t>https://artportalen.se/Sighting/130659216</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136480812</v>
+        <v>136480614</v>
       </c>
       <c r="B7" t="n">
-        <v>58731</v>
+        <v>58169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1331,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,10 +1364,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707254</v>
+        <v>707152</v>
       </c>
       <c r="R7" t="n">
-        <v>6624731</v>
+        <v>6624756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1399,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:29</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1409,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:29</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,7 +1439,648 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136480614</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136480594</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>707188</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6624740</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Fågelinventering Sika 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480594</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136480597</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>707213</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6624684</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Fågelinventering Sika 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480597</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136480812</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58731</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>707254</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6624731</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Fågelinventering Sika 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136480812</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137154384</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56887</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sika, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>707174</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6624767</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>NVI Sika 4:37</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137154384</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137154386</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56866</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sika, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>707174</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6624767</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>NVI Sika 4:37</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137154386</t>
         </is>
       </c>
     </row>
@@ -1421,6 +2092,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>137154287</v>
       </c>
       <c r="B3" t="n">
-        <v>56882</v>
+        <v>56895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>137154292</v>
       </c>
       <c r="B4" t="n">
-        <v>56882</v>
+        <v>56895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>137154385</v>
       </c>
       <c r="B5" t="n">
-        <v>56882</v>
+        <v>56895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137154384</v>
       </c>
       <c r="B11" t="n">
-        <v>56887</v>
+        <v>56900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>137154386</v>
       </c>
       <c r="B12" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>137154287</v>
       </c>
       <c r="B3" t="n">
-        <v>56895</v>
+        <v>56897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>137154292</v>
       </c>
       <c r="B4" t="n">
-        <v>56895</v>
+        <v>56897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>137154385</v>
       </c>
       <c r="B5" t="n">
-        <v>56895</v>
+        <v>56897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137154384</v>
       </c>
       <c r="B11" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>137154386</v>
       </c>
       <c r="B12" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -843,11 +843,7 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -978,11 +974,7 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -1113,11 +1105,7 @@
           <t>registreringar</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>autobox med tidsexpansion</t>
@@ -1858,11 +1846,7 @@
           <t>registreringar</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>autobox med tidsexpansion</t>
@@ -1989,11 +1973,7 @@
           <t>registreringar</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>autobox med tidsexpansion</t>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>137154287</v>
       </c>
       <c r="B3" t="n">
-        <v>56897</v>
+        <v>56907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>137154292</v>
       </c>
       <c r="B4" t="n">
-        <v>56897</v>
+        <v>56907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>137154385</v>
       </c>
       <c r="B5" t="n">
-        <v>56897</v>
+        <v>56907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137154384</v>
       </c>
       <c r="B11" t="n">
-        <v>56902</v>
+        <v>56912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>137154386</v>
       </c>
       <c r="B12" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>137154287</v>
       </c>
       <c r="B3" t="n">
-        <v>56907</v>
+        <v>56908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>137154292</v>
       </c>
       <c r="B4" t="n">
-        <v>56907</v>
+        <v>56908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>137154385</v>
       </c>
       <c r="B5" t="n">
-        <v>56907</v>
+        <v>56908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137154384</v>
       </c>
       <c r="B11" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>137154386</v>
       </c>
       <c r="B12" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>137154287</v>
       </c>
       <c r="B3" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>137154292</v>
       </c>
       <c r="B4" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>137154385</v>
       </c>
       <c r="B5" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137154384</v>
       </c>
       <c r="B11" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>137154386</v>
       </c>
       <c r="B12" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
